--- a/src/Bangus_Distribution_Cleaned.xlsx
+++ b/src/Bangus_Distribution_Cleaned.xlsx
@@ -1,15 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView windowWidth="23040" windowHeight="9708"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="we0U/SnQL8g47O9UjOKliBgN6Wl9y4YJXD6y10VFrHY="/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -426,69 +437,922 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
-    <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="6">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="42" formatCode="_-&quot;₱&quot;* #,##0_-;\-&quot;₱&quot;* #,##0_-;_-&quot;₱&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;₱&quot;* #,##0.00_-;\-&quot;₱&quot;* #,##0.00_-;_-&quot;₱&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="mm/dd/yyyy"/>
+    <numFmt numFmtId="177" formatCode="m/d/yyyy"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="22">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="1">
-    <border/>
+  <borders count="9">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -678,29 +1542,29 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I1000"/>
+  <sheetFormatPr defaultColWidth="14.4259259259259" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="19.43"/>
-    <col customWidth="1" min="2" max="2" width="21.71"/>
-    <col customWidth="1" min="3" max="3" width="20.14"/>
-    <col customWidth="1" min="4" max="4" width="15.71"/>
-    <col customWidth="1" min="5" max="5" width="15.29"/>
-    <col customWidth="1" min="6" max="6" width="13.57"/>
-    <col customWidth="1" min="7" max="7" width="16.29"/>
-    <col customWidth="1" min="8" max="8" width="20.14"/>
-    <col customWidth="1" min="9" max="9" width="20.57"/>
-    <col customWidth="1" min="10" max="26" width="8.71"/>
+    <col min="1" max="1" width="19.4259259259259" customWidth="1"/>
+    <col min="2" max="2" width="21.712962962963" customWidth="1"/>
+    <col min="3" max="3" width="20.1388888888889" customWidth="1"/>
+    <col min="4" max="4" width="15.712962962963" customWidth="1"/>
+    <col min="5" max="5" width="15.287037037037" customWidth="1"/>
+    <col min="6" max="6" width="13.5740740740741" customWidth="1"/>
+    <col min="7" max="7" width="16.287037037037" customWidth="1"/>
+    <col min="8" max="8" width="20.1388888888889" customWidth="1"/>
+    <col min="9" max="9" width="20.5740740740741" customWidth="1"/>
+    <col min="10" max="26" width="8.71296296296296" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="14.4" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -729,7 +1593,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="14.4" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -746,16 +1610,16 @@
         <v>13</v>
       </c>
       <c r="F2" s="1">
-        <v>17000.0</v>
+        <v>17000</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="1">
-        <v>6199.0</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="I2" s="2">
+        <v>6275</v>
+      </c>
+    </row>
+    <row r="3" ht="14.4" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
@@ -772,23 +1636,23 @@
         <v>19</v>
       </c>
       <c r="F3" s="1">
-        <v>25000.0</v>
+        <v>25000</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="1">
-        <v>9116.0</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="I3" s="3">
+        <v>8814</v>
+      </c>
+    </row>
+    <row r="4" ht="14.4" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" t="s">
         <v>17</v>
       </c>
       <c r="D4" s="1" t="s">
@@ -798,23 +1662,23 @@
         <v>19</v>
       </c>
       <c r="F4" s="1">
-        <v>5000.0</v>
+        <v>5000</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I4" s="1">
-        <v>1823.0</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="I4" s="3">
+        <v>1883</v>
+      </c>
+    </row>
+    <row r="5" ht="14.4" spans="1:9">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" t="s">
         <v>23</v>
       </c>
       <c r="D5" s="1" t="s">
@@ -824,16 +1688,16 @@
         <v>25</v>
       </c>
       <c r="F5" s="1">
-        <v>3000.0</v>
+        <v>3000</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I5" s="1">
-        <v>1093.0</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="I5" s="3">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="6" ht="14.4" spans="1:9">
       <c r="A6" s="1" t="s">
         <v>21</v>
       </c>
@@ -850,16 +1714,16 @@
         <v>25</v>
       </c>
       <c r="F6" s="1">
-        <v>3000.0</v>
+        <v>3000</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I6" s="1">
-        <v>1093.0</v>
-      </c>
-    </row>
-    <row r="7">
+      <c r="I6" s="3">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="7" ht="14.4" spans="1:9">
       <c r="A7" s="1" t="s">
         <v>28</v>
       </c>
@@ -876,16 +1740,16 @@
         <v>19</v>
       </c>
       <c r="F7" s="1">
-        <v>40000.0</v>
+        <v>40000</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I7" s="1">
-        <v>14586.0</v>
-      </c>
-    </row>
-    <row r="8">
+      <c r="I7" s="3">
+        <v>14815</v>
+      </c>
+    </row>
+    <row r="8" ht="14.4" spans="1:9">
       <c r="A8" s="1" t="s">
         <v>32</v>
       </c>
@@ -902,16 +1766,16 @@
         <v>13</v>
       </c>
       <c r="F8" s="1">
-        <v>6000.0</v>
+        <v>6000</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I8" s="1">
-        <v>2187.0</v>
-      </c>
-    </row>
-    <row r="9">
+      <c r="I8" s="3">
+        <v>2119</v>
+      </c>
+    </row>
+    <row r="9" ht="14.4" spans="1:9">
       <c r="A9" s="1" t="s">
         <v>32</v>
       </c>
@@ -928,16 +1792,16 @@
         <v>13</v>
       </c>
       <c r="F9" s="1">
-        <v>6000.0</v>
+        <v>6000</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I9" s="1">
-        <v>2187.0</v>
-      </c>
-    </row>
-    <row r="10">
+      <c r="I9" s="3">
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="10" ht="14.4" spans="1:9">
       <c r="A10" s="1" t="s">
         <v>32</v>
       </c>
@@ -954,16 +1818,16 @@
         <v>19</v>
       </c>
       <c r="F10" s="1">
-        <v>40000.0</v>
+        <v>40000</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I10" s="1">
-        <v>14586.0</v>
-      </c>
-    </row>
-    <row r="11">
+      <c r="I10" s="3">
+        <v>14180</v>
+      </c>
+    </row>
+    <row r="11" ht="14.4" spans="1:9">
       <c r="A11" s="1" t="s">
         <v>32</v>
       </c>
@@ -980,16 +1844,16 @@
         <v>13</v>
       </c>
       <c r="F11" s="1">
-        <v>21000.0</v>
+        <v>21000</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I11" s="1">
-        <v>7657.0</v>
-      </c>
-    </row>
-    <row r="12">
+      <c r="I11" s="3">
+        <v>7869</v>
+      </c>
+    </row>
+    <row r="12" ht="14.4" spans="1:9">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -1006,16 +1870,16 @@
         <v>19</v>
       </c>
       <c r="F12" s="1">
-        <v>3500.0</v>
+        <v>3500</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I12" s="1">
-        <v>1276.0</v>
-      </c>
-    </row>
-    <row r="13">
+      <c r="I12" s="3">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="13" ht="14.4" spans="1:9">
       <c r="A13" s="1" t="s">
         <v>44</v>
       </c>
@@ -1032,16 +1896,16 @@
         <v>19</v>
       </c>
       <c r="F13" s="1">
-        <v>35000.0</v>
+        <v>35000</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I13" s="1">
-        <v>12762.0</v>
-      </c>
-    </row>
-    <row r="14">
+      <c r="I13" s="3">
+        <v>12457</v>
+      </c>
+    </row>
+    <row r="14" ht="14.4" spans="1:9">
       <c r="A14" s="1" t="s">
         <v>44</v>
       </c>
@@ -1058,16 +1922,16 @@
         <v>19</v>
       </c>
       <c r="F14" s="1">
-        <v>35000.0</v>
+        <v>35000</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I14" s="1">
-        <v>12762.0</v>
-      </c>
-    </row>
-    <row r="15">
+      <c r="I14" s="3">
+        <v>12406</v>
+      </c>
+    </row>
+    <row r="15" ht="14.4" spans="1:9">
       <c r="A15" s="1" t="s">
         <v>44</v>
       </c>
@@ -1084,16 +1948,16 @@
         <v>19</v>
       </c>
       <c r="F15" s="1">
-        <v>30000.0</v>
+        <v>30000</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I15" s="1">
-        <v>10939.0</v>
-      </c>
-    </row>
-    <row r="16">
+      <c r="I15" s="3">
+        <v>10845</v>
+      </c>
+    </row>
+    <row r="16" ht="14.4" spans="1:9">
       <c r="A16" s="1" t="s">
         <v>44</v>
       </c>
@@ -1110,16 +1974,16 @@
         <v>19</v>
       </c>
       <c r="F16" s="1">
-        <v>30000.0</v>
+        <v>30000</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I16" s="1">
-        <v>10939.0</v>
-      </c>
-    </row>
-    <row r="17">
+      <c r="I16" s="3">
+        <v>11082</v>
+      </c>
+    </row>
+    <row r="17" ht="14.4" spans="1:9">
       <c r="A17" s="1" t="s">
         <v>44</v>
       </c>
@@ -1136,18 +2000,18 @@
         <v>19</v>
       </c>
       <c r="F17" s="1">
-        <v>30000.0</v>
+        <v>30000</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I17" s="1">
-        <v>10939.0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3">
-        <v>45202.0</v>
+      <c r="I17" s="3">
+        <v>10742</v>
+      </c>
+    </row>
+    <row r="18" ht="14.4" spans="1:9">
+      <c r="A18" s="4">
+        <v>45202</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>50</v>
@@ -1162,16 +2026,16 @@
         <v>19</v>
       </c>
       <c r="F18" s="1">
-        <v>35000.0</v>
+        <v>35000</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I18" s="1">
-        <v>12762.0</v>
-      </c>
-    </row>
-    <row r="19">
+      <c r="I18" s="3">
+        <v>13079</v>
+      </c>
+    </row>
+    <row r="19" ht="14.4" spans="1:9">
       <c r="A19" s="1" t="s">
         <v>51</v>
       </c>
@@ -1188,16 +2052,16 @@
         <v>19</v>
       </c>
       <c r="F19" s="1">
-        <v>30000.0</v>
+        <v>30000</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I19" s="1">
-        <v>10939.0</v>
-      </c>
-    </row>
-    <row r="20">
+      <c r="I19" s="3">
+        <v>10851</v>
+      </c>
+    </row>
+    <row r="20" ht="14.4" spans="1:9">
       <c r="A20" s="1" t="s">
         <v>51</v>
       </c>
@@ -1214,18 +2078,18 @@
         <v>19</v>
       </c>
       <c r="F20" s="1">
-        <v>25000.0</v>
+        <v>25000</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I20" s="1">
-        <v>9116.0</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="3">
-        <v>45202.0</v>
+      <c r="I20" s="3">
+        <v>8941</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1" spans="1:9">
+      <c r="A21" s="4">
+        <v>45202</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>55</v>
@@ -1240,16 +2104,16 @@
         <v>19</v>
       </c>
       <c r="F21" s="1">
-        <v>40000.0</v>
+        <v>40000</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I21" s="1">
-        <v>14586.0</v>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
+      <c r="I21" s="3">
+        <v>14301</v>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1" spans="1:9">
       <c r="A22" s="1" t="s">
         <v>51</v>
       </c>
@@ -1266,17 +2130,17 @@
         <v>19</v>
       </c>
       <c r="F22" s="1">
-        <v>30000.0</v>
+        <v>30000</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I22" s="1">
-        <v>10939.0</v>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="4" t="s">
+      <c r="I22" s="3">
+        <v>11159</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" spans="1:9">
+      <c r="A23" s="5" t="s">
         <v>57</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -1292,16 +2156,16 @@
         <v>19</v>
       </c>
       <c r="F23" s="1">
-        <v>50000.0</v>
+        <v>50000</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I23" s="1">
-        <v>18232.0</v>
-      </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
+      <c r="I23" s="3">
+        <v>18312</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1" spans="1:9">
       <c r="A24" s="1" t="s">
         <v>57</v>
       </c>
@@ -1318,16 +2182,16 @@
         <v>19</v>
       </c>
       <c r="F24" s="1">
-        <v>30000.0</v>
+        <v>30000</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I24" s="1">
-        <v>10939.0</v>
-      </c>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
+      <c r="I24" s="3">
+        <v>10959</v>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1" spans="1:9">
       <c r="A25" s="1" t="s">
         <v>62</v>
       </c>
@@ -1344,16 +2208,16 @@
         <v>19</v>
       </c>
       <c r="F25" s="1">
-        <v>3000.0</v>
+        <v>3000</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I25" s="1">
-        <v>1093.0</v>
-      </c>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
+      <c r="I25" s="3">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1" spans="1:9">
       <c r="A26" s="1" t="s">
         <v>62</v>
       </c>
@@ -1370,16 +2234,16 @@
         <v>19</v>
       </c>
       <c r="F26" s="1">
-        <v>10000.0</v>
+        <v>10000</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I26" s="1">
-        <v>3646.0</v>
-      </c>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
+      <c r="I26" s="3">
+        <v>3652</v>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1" spans="1:9">
       <c r="A27" s="1" t="s">
         <v>62</v>
       </c>
@@ -1396,16 +2260,16 @@
         <v>19</v>
       </c>
       <c r="F27" s="1">
-        <v>8000.0</v>
+        <v>8000</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I27" s="1">
-        <v>2917.0</v>
-      </c>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
+      <c r="I27" s="3">
+        <v>3011</v>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1" spans="1:9">
       <c r="A28" s="1" t="s">
         <v>62</v>
       </c>
@@ -1422,16 +2286,16 @@
         <v>19</v>
       </c>
       <c r="F28" s="1">
-        <v>5000.0</v>
+        <v>5000</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I28" s="1">
-        <v>1823.0</v>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
+      <c r="I28" s="3">
+        <v>1822</v>
+      </c>
+    </row>
+    <row r="29" ht="15.75" customHeight="1" spans="1:9">
       <c r="A29" s="1" t="s">
         <v>62</v>
       </c>
@@ -1448,16 +2312,16 @@
         <v>19</v>
       </c>
       <c r="F29" s="1">
-        <v>5000.0</v>
+        <v>5000</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I29" s="1">
-        <v>1823.0</v>
-      </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
+      <c r="I29" s="3">
+        <v>1845</v>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1" spans="1:9">
       <c r="A30" s="1" t="s">
         <v>62</v>
       </c>
@@ -1474,16 +2338,16 @@
         <v>19</v>
       </c>
       <c r="F30" s="1">
-        <v>6000.0</v>
+        <v>6000</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I30" s="1">
-        <v>2187.0</v>
-      </c>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
+      <c r="I30" s="3">
+        <v>2257</v>
+      </c>
+    </row>
+    <row r="31" ht="15.75" customHeight="1" spans="1:9">
       <c r="A31" s="1" t="s">
         <v>62</v>
       </c>
@@ -1500,16 +2364,16 @@
         <v>19</v>
       </c>
       <c r="F31" s="1">
-        <v>6000.0</v>
+        <v>6000</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I31" s="1">
-        <v>2187.0</v>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
+      <c r="I31" s="3">
+        <v>2168</v>
+      </c>
+    </row>
+    <row r="32" ht="15.75" customHeight="1" spans="1:9">
       <c r="A32" s="1" t="s">
         <v>62</v>
       </c>
@@ -1526,16 +2390,16 @@
         <v>19</v>
       </c>
       <c r="F32" s="1">
-        <v>5000.0</v>
+        <v>5000</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I32" s="1">
-        <v>1823.0</v>
-      </c>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
+      <c r="I32" s="3">
+        <v>1855</v>
+      </c>
+    </row>
+    <row r="33" ht="15.75" customHeight="1" spans="1:9">
       <c r="A33" s="1" t="s">
         <v>62</v>
       </c>
@@ -1552,16 +2416,16 @@
         <v>19</v>
       </c>
       <c r="F33" s="1">
-        <v>6000.0</v>
+        <v>6000</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I33" s="1">
-        <v>2187.0</v>
-      </c>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
+      <c r="I33" s="3">
+        <v>2231</v>
+      </c>
+    </row>
+    <row r="34" ht="15.75" customHeight="1" spans="1:9">
       <c r="A34" s="1" t="s">
         <v>62</v>
       </c>
@@ -1578,16 +2442,16 @@
         <v>19</v>
       </c>
       <c r="F34" s="1">
-        <v>7000.0</v>
+        <v>7000</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I34" s="1">
-        <v>2552.0</v>
-      </c>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
+      <c r="I34" s="3">
+        <v>2554</v>
+      </c>
+    </row>
+    <row r="35" ht="15.75" customHeight="1" spans="1:9">
       <c r="A35" s="1" t="s">
         <v>62</v>
       </c>
@@ -1604,16 +2468,16 @@
         <v>19</v>
       </c>
       <c r="F35" s="1">
-        <v>6500.0</v>
+        <v>6500</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I35" s="1">
-        <v>2370.0</v>
-      </c>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
+      <c r="I35" s="3">
+        <v>2335</v>
+      </c>
+    </row>
+    <row r="36" ht="15.75" customHeight="1" spans="1:9">
       <c r="A36" s="1" t="s">
         <v>62</v>
       </c>
@@ -1630,16 +2494,16 @@
         <v>19</v>
       </c>
       <c r="F36" s="1">
-        <v>5000.0</v>
+        <v>5000</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I36" s="1">
-        <v>1823.0</v>
-      </c>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
+      <c r="I36" s="3">
+        <v>1762</v>
+      </c>
+    </row>
+    <row r="37" ht="15.75" customHeight="1" spans="1:9">
       <c r="A37" s="1" t="s">
         <v>62</v>
       </c>
@@ -1656,16 +2520,16 @@
         <v>19</v>
       </c>
       <c r="F37" s="1">
-        <v>6500.0</v>
+        <v>6500</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I37" s="1">
-        <v>2370.0</v>
-      </c>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
+      <c r="I37" s="3">
+        <v>2301</v>
+      </c>
+    </row>
+    <row r="38" ht="15.75" customHeight="1" spans="1:9">
       <c r="A38" s="1" t="s">
         <v>62</v>
       </c>
@@ -1682,16 +2546,16 @@
         <v>19</v>
       </c>
       <c r="F38" s="1">
-        <v>6000.0</v>
+        <v>6000</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I38" s="1">
-        <v>2187.0</v>
-      </c>
-    </row>
-    <row r="39" ht="15.75" customHeight="1">
+      <c r="I38" s="3">
+        <v>2141</v>
+      </c>
+    </row>
+    <row r="39" ht="15.75" customHeight="1" spans="1:9">
       <c r="A39" s="1" t="s">
         <v>62</v>
       </c>
@@ -1708,16 +2572,16 @@
         <v>19</v>
       </c>
       <c r="F39" s="1">
-        <v>10000.0</v>
+        <v>10000</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I39" s="1">
-        <v>3646.0</v>
-      </c>
-    </row>
-    <row r="40" ht="15.75" customHeight="1">
+      <c r="I39" s="3">
+        <v>3773</v>
+      </c>
+    </row>
+    <row r="40" ht="15.75" customHeight="1" spans="1:9">
       <c r="A40" s="1" t="s">
         <v>62</v>
       </c>
@@ -1734,16 +2598,16 @@
         <v>19</v>
       </c>
       <c r="F40" s="1">
-        <v>8000.0</v>
+        <v>8000</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I40" s="1">
-        <v>2917.0</v>
-      </c>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
+      <c r="I40" s="3">
+        <v>2951</v>
+      </c>
+    </row>
+    <row r="41" ht="15.75" customHeight="1" spans="1:9">
       <c r="A41" s="1" t="s">
         <v>62</v>
       </c>
@@ -1760,16 +2624,16 @@
         <v>19</v>
       </c>
       <c r="F41" s="1">
-        <v>2000.0</v>
+        <v>2000</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I41" s="1">
-        <v>729.0</v>
-      </c>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
+      <c r="I41" s="3">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="42" ht="15.75" customHeight="1" spans="1:9">
       <c r="A42" s="1" t="s">
         <v>62</v>
       </c>
@@ -1786,16 +2650,16 @@
         <v>19</v>
       </c>
       <c r="F42" s="1">
-        <v>3000.0</v>
+        <v>3000</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I42" s="1">
-        <v>1093.0</v>
-      </c>
-    </row>
-    <row r="43" ht="15.75" customHeight="1">
+      <c r="I42" s="3">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="43" ht="15.75" customHeight="1" spans="1:9">
       <c r="A43" s="1" t="s">
         <v>62</v>
       </c>
@@ -1812,16 +2676,16 @@
         <v>19</v>
       </c>
       <c r="F43" s="1">
-        <v>3000.0</v>
+        <v>3000</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I43" s="1">
-        <v>1095.0</v>
-      </c>
-    </row>
-    <row r="44" ht="15.75" customHeight="1">
+      <c r="I43" s="3">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="44" ht="15.75" customHeight="1" spans="1:9">
       <c r="A44" s="1" t="s">
         <v>62</v>
       </c>
@@ -1838,16 +2702,16 @@
         <v>19</v>
       </c>
       <c r="F44" s="1">
-        <v>3000.0</v>
+        <v>3000</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I44" s="1">
-        <v>1093.0</v>
-      </c>
-    </row>
-    <row r="45" ht="15.75" customHeight="1">
+      <c r="I44" s="3">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="45" ht="15.75" customHeight="1" spans="1:9">
       <c r="A45" s="1" t="s">
         <v>62</v>
       </c>
@@ -1864,16 +2728,16 @@
         <v>19</v>
       </c>
       <c r="F45" s="1">
-        <v>5000.0</v>
+        <v>5000</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I45" s="1">
-        <v>1823.0</v>
-      </c>
-    </row>
-    <row r="46" ht="15.75" customHeight="1">
+      <c r="I45" s="3">
+        <v>1868</v>
+      </c>
+    </row>
+    <row r="46" ht="15.75" customHeight="1" spans="1:9">
       <c r="A46" s="1" t="s">
         <v>62</v>
       </c>
@@ -1890,16 +2754,16 @@
         <v>19</v>
       </c>
       <c r="F46" s="1">
-        <v>4000.0</v>
+        <v>4000</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I46" s="1">
-        <v>1458.0</v>
-      </c>
-    </row>
-    <row r="47" ht="15.75" customHeight="1">
+      <c r="I46" s="3">
+        <v>1477</v>
+      </c>
+    </row>
+    <row r="47" ht="15.75" customHeight="1" spans="1:9">
       <c r="A47" s="1" t="s">
         <v>62</v>
       </c>
@@ -1916,16 +2780,16 @@
         <v>19</v>
       </c>
       <c r="F47" s="1">
-        <v>10000.0</v>
+        <v>10000</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I47" s="1">
-        <v>3646.0</v>
-      </c>
-    </row>
-    <row r="48" ht="15.75" customHeight="1">
+      <c r="I47" s="3">
+        <v>3646</v>
+      </c>
+    </row>
+    <row r="48" ht="15.75" customHeight="1" spans="1:9">
       <c r="A48" s="1" t="s">
         <v>62</v>
       </c>
@@ -1942,16 +2806,16 @@
         <v>19</v>
       </c>
       <c r="F48" s="1">
-        <v>18600.0</v>
+        <v>18600</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I48" s="1">
-        <v>6782.0</v>
-      </c>
-    </row>
-    <row r="49" ht="15.75" customHeight="1">
+      <c r="I48" s="3">
+        <v>6561</v>
+      </c>
+    </row>
+    <row r="49" ht="15.75" customHeight="1" spans="1:9">
       <c r="A49" s="1" t="s">
         <v>89</v>
       </c>
@@ -1968,16 +2832,16 @@
         <v>25</v>
       </c>
       <c r="F49" s="1">
-        <v>6000.0</v>
+        <v>6000</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I49" s="1">
-        <v>2187.0</v>
-      </c>
-    </row>
-    <row r="50" ht="15.75" customHeight="1">
+      <c r="I49" s="3">
+        <v>2150</v>
+      </c>
+    </row>
+    <row r="50" ht="15.75" customHeight="1" spans="1:9">
       <c r="A50" s="1" t="s">
         <v>89</v>
       </c>
@@ -1994,16 +2858,16 @@
         <v>25</v>
       </c>
       <c r="F50" s="1">
-        <v>5000.0</v>
+        <v>5000</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I50" s="1">
-        <v>1823.0</v>
-      </c>
-    </row>
-    <row r="51" ht="15.75" customHeight="1">
+      <c r="I50" s="3">
+        <v>1810</v>
+      </c>
+    </row>
+    <row r="51" ht="15.75" customHeight="1" spans="1:9">
       <c r="A51" s="1" t="s">
         <v>89</v>
       </c>
@@ -2020,16 +2884,16 @@
         <v>25</v>
       </c>
       <c r="F51" s="1">
-        <v>3000.0</v>
+        <v>3000</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I51" s="1">
-        <v>1093.0</v>
-      </c>
-    </row>
-    <row r="52" ht="15.75" customHeight="1">
+      <c r="I51" s="3">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="52" ht="15.75" customHeight="1" spans="1:9">
       <c r="A52" s="1" t="s">
         <v>89</v>
       </c>
@@ -2046,16 +2910,16 @@
         <v>25</v>
       </c>
       <c r="F52" s="1">
-        <v>3000.0</v>
+        <v>3000</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I52" s="1">
-        <v>1093.0</v>
-      </c>
-    </row>
-    <row r="53" ht="15.75" customHeight="1">
+      <c r="I52" s="3">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="53" ht="15.75" customHeight="1" spans="1:9">
       <c r="A53" s="1" t="s">
         <v>89</v>
       </c>
@@ -2072,16 +2936,16 @@
         <v>25</v>
       </c>
       <c r="F53" s="1">
-        <v>3000.0</v>
+        <v>3000</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I53" s="1">
-        <v>1093.0</v>
-      </c>
-    </row>
-    <row r="54" ht="15.75" customHeight="1">
+      <c r="I53" s="3">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="54" ht="15.75" customHeight="1" spans="1:9">
       <c r="A54" s="1" t="s">
         <v>89</v>
       </c>
@@ -2098,16 +2962,16 @@
         <v>25</v>
       </c>
       <c r="F54" s="1">
-        <v>6000.0</v>
+        <v>6000</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I54" s="1">
-        <v>2187.0</v>
-      </c>
-    </row>
-    <row r="55" ht="15.75" customHeight="1">
+      <c r="I54" s="3">
+        <v>2168</v>
+      </c>
+    </row>
+    <row r="55" ht="15.75" customHeight="1" spans="1:9">
       <c r="A55" s="1" t="s">
         <v>89</v>
       </c>
@@ -2124,16 +2988,16 @@
         <v>25</v>
       </c>
       <c r="F55" s="1">
-        <v>40000.0</v>
+        <v>40000</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I55" s="1">
-        <v>14586.0</v>
-      </c>
-    </row>
-    <row r="56" ht="15.75" customHeight="1">
+      <c r="I55" s="3">
+        <v>14041</v>
+      </c>
+    </row>
+    <row r="56" ht="15.75" customHeight="1" spans="1:9">
       <c r="A56" s="1" t="s">
         <v>89</v>
       </c>
@@ -2150,16 +3014,16 @@
         <v>25</v>
       </c>
       <c r="F56" s="1">
-        <v>40000.0</v>
+        <v>40000</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I56" s="1">
-        <v>14586.0</v>
-      </c>
-    </row>
-    <row r="57" ht="15.75" customHeight="1">
+      <c r="I56" s="3">
+        <v>14323</v>
+      </c>
+    </row>
+    <row r="57" ht="15.75" customHeight="1" spans="1:9">
       <c r="A57" s="1" t="s">
         <v>89</v>
       </c>
@@ -2176,16 +3040,16 @@
         <v>25</v>
       </c>
       <c r="F57" s="1">
-        <v>3000.0</v>
+        <v>3000</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I57" s="1">
-        <v>1093.0</v>
-      </c>
-    </row>
-    <row r="58" ht="15.75" customHeight="1">
+      <c r="I57" s="3">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="58" ht="15.75" customHeight="1" spans="1:9">
       <c r="A58" s="1" t="s">
         <v>89</v>
       </c>
@@ -2202,16 +3066,16 @@
         <v>25</v>
       </c>
       <c r="F58" s="1">
-        <v>3000.0</v>
+        <v>3000</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I58" s="1">
-        <v>1095.0</v>
-      </c>
-    </row>
-    <row r="59" ht="15.75" customHeight="1">
+      <c r="I58" s="3">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="59" ht="15.75" customHeight="1" spans="1:9">
       <c r="A59" s="1" t="s">
         <v>89</v>
       </c>
@@ -2228,16 +3092,16 @@
         <v>25</v>
       </c>
       <c r="F59" s="1">
-        <v>3000.0</v>
+        <v>3000</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I59" s="1">
-        <v>1093.0</v>
-      </c>
-    </row>
-    <row r="60" ht="15.75" customHeight="1">
+      <c r="I59" s="3">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="60" ht="15.75" customHeight="1" spans="1:9">
       <c r="A60" s="1" t="s">
         <v>89</v>
       </c>
@@ -2254,16 +3118,16 @@
         <v>25</v>
       </c>
       <c r="F60" s="1">
-        <v>5000.0</v>
+        <v>5000</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I60" s="1">
-        <v>1823.0</v>
-      </c>
-    </row>
-    <row r="61" ht="15.75" customHeight="1">
+      <c r="I60" s="3">
+        <v>1798</v>
+      </c>
+    </row>
+    <row r="61" ht="15.75" customHeight="1" spans="1:9">
       <c r="A61" s="1" t="s">
         <v>104</v>
       </c>
@@ -2280,16 +3144,16 @@
         <v>13</v>
       </c>
       <c r="F61" s="1">
-        <v>30000.0</v>
+        <v>30000</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I61" s="1">
-        <v>10939.0</v>
-      </c>
-    </row>
-    <row r="62" ht="15.75" customHeight="1">
+      <c r="I61" s="3">
+        <v>10552</v>
+      </c>
+    </row>
+    <row r="62" ht="15.75" customHeight="1" spans="1:9">
       <c r="A62" s="1" t="s">
         <v>104</v>
       </c>
@@ -2306,16 +3170,16 @@
         <v>13</v>
       </c>
       <c r="F62" s="1">
-        <v>30000.0</v>
+        <v>30000</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I62" s="1">
-        <v>11949.0</v>
-      </c>
-    </row>
-    <row r="63" ht="15.75" customHeight="1">
+      <c r="I62" s="3">
+        <v>10715</v>
+      </c>
+    </row>
+    <row r="63" ht="15.75" customHeight="1" spans="1:9">
       <c r="A63" s="1" t="s">
         <v>104</v>
       </c>
@@ -2332,16 +3196,16 @@
         <v>13</v>
       </c>
       <c r="F63" s="1">
-        <v>30000.0</v>
+        <v>30000</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I63" s="1">
-        <v>10939.0</v>
-      </c>
-    </row>
-    <row r="64" ht="15.75" customHeight="1">
+      <c r="I63" s="3">
+        <v>11224</v>
+      </c>
+    </row>
+    <row r="64" ht="15.75" customHeight="1" spans="1:9">
       <c r="A64" s="1" t="s">
         <v>104</v>
       </c>
@@ -2358,16 +3222,16 @@
         <v>13</v>
       </c>
       <c r="F64" s="1">
-        <v>33400.0</v>
+        <v>33400</v>
       </c>
       <c r="G64" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I64" s="1">
-        <v>12179.0</v>
-      </c>
-    </row>
-    <row r="65" ht="15.75" customHeight="1">
+      <c r="I64" s="3">
+        <v>11822</v>
+      </c>
+    </row>
+    <row r="65" ht="15.75" customHeight="1" spans="1:9">
       <c r="A65" s="1" t="s">
         <v>104</v>
       </c>
@@ -2384,16 +3248,16 @@
         <v>115</v>
       </c>
       <c r="F65" s="1">
-        <v>8000.0</v>
+        <v>8000</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I65" s="1">
-        <v>2917.0</v>
-      </c>
-    </row>
-    <row r="66" ht="15.75" customHeight="1">
+      <c r="I65" s="3">
+        <v>2830</v>
+      </c>
+    </row>
+    <row r="66" ht="15.75" customHeight="1" spans="1:9">
       <c r="A66" s="1" t="s">
         <v>116</v>
       </c>
@@ -2410,16 +3274,16 @@
         <v>13</v>
       </c>
       <c r="F66" s="1">
-        <v>30000.0</v>
+        <v>30000</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I66" s="1">
-        <v>10939.0</v>
-      </c>
-    </row>
-    <row r="67" ht="15.75" customHeight="1">
+      <c r="I66" s="3">
+        <v>11340</v>
+      </c>
+    </row>
+    <row r="67" ht="15.75" customHeight="1" spans="1:9">
       <c r="A67" s="1" t="s">
         <v>116</v>
       </c>
@@ -2436,18 +3300,18 @@
         <v>13</v>
       </c>
       <c r="F67" s="1">
-        <v>30000.0</v>
+        <v>30000</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I67" s="1">
-        <v>10945.0</v>
-      </c>
-    </row>
-    <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="5">
-        <v>45273.0</v>
+      <c r="I67" s="3">
+        <v>10894</v>
+      </c>
+    </row>
+    <row r="68" ht="15.75" customHeight="1" spans="1:9">
+      <c r="A68" s="6">
+        <v>45273</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>120</v>
@@ -2462,18 +3326,18 @@
         <v>19</v>
       </c>
       <c r="F68" s="1">
-        <v>50000.0</v>
+        <v>50000</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I68" s="1">
-        <v>18232.0</v>
-      </c>
-    </row>
-    <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="5">
-        <v>45273.0</v>
+      <c r="I68" s="3">
+        <v>18347</v>
+      </c>
+    </row>
+    <row r="69" ht="15.75" customHeight="1" spans="1:9">
+      <c r="A69" s="6">
+        <v>45273</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>121</v>
@@ -2488,18 +3352,18 @@
         <v>19</v>
       </c>
       <c r="F69" s="1">
-        <v>50000.0</v>
+        <v>50000</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I69" s="1">
-        <v>18223.0</v>
-      </c>
-    </row>
-    <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="5">
-        <v>45274.0</v>
+      <c r="I69" s="3">
+        <v>17638</v>
+      </c>
+    </row>
+    <row r="70" ht="15.75" customHeight="1" spans="1:9">
+      <c r="A70" s="6">
+        <v>45274</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>122</v>
@@ -2514,18 +3378,18 @@
         <v>19</v>
       </c>
       <c r="F70" s="1">
-        <v>35000.0</v>
+        <v>35000</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I70" s="1">
-        <v>12762.0</v>
-      </c>
-    </row>
-    <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="5">
-        <v>45274.0</v>
+      <c r="I70" s="3">
+        <v>13024</v>
+      </c>
+    </row>
+    <row r="71" ht="15.75" customHeight="1" spans="1:9">
+      <c r="A71" s="6">
+        <v>45274</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>123</v>
@@ -2540,18 +3404,18 @@
         <v>126</v>
       </c>
       <c r="F71" s="1">
-        <v>30000.0</v>
+        <v>30000</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I71" s="1">
-        <v>10939.0</v>
-      </c>
-    </row>
-    <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="5">
-        <v>45274.0</v>
+      <c r="I71" s="3">
+        <v>11155</v>
+      </c>
+    </row>
+    <row r="72" ht="15.75" customHeight="1" spans="1:9">
+      <c r="A72" s="6">
+        <v>45274</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>127</v>
@@ -2566,18 +3430,18 @@
         <v>126</v>
       </c>
       <c r="F72" s="1">
-        <v>50000.0</v>
+        <v>50000</v>
       </c>
       <c r="G72" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I72" s="1">
-        <v>18235.0</v>
-      </c>
-    </row>
-    <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="5">
-        <v>45274.0</v>
+      <c r="I72" s="3">
+        <v>18375</v>
+      </c>
+    </row>
+    <row r="73" ht="15.75" customHeight="1" spans="1:9">
+      <c r="A73" s="6">
+        <v>45274</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>128</v>
@@ -2592,18 +3456,18 @@
         <v>126</v>
       </c>
       <c r="F73" s="1">
-        <v>50000.0</v>
+        <v>50000</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I73" s="1">
-        <v>18232.0</v>
-      </c>
-    </row>
-    <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="5">
-        <v>45276.0</v>
+      <c r="I73" s="3">
+        <v>18062</v>
+      </c>
+    </row>
+    <row r="74" ht="15.75" customHeight="1" spans="1:9">
+      <c r="A74" s="6">
+        <v>45276</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>129</v>
@@ -2618,18 +3482,18 @@
         <v>25</v>
       </c>
       <c r="F74" s="1">
-        <v>50000.0</v>
+        <v>50000</v>
       </c>
       <c r="G74" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I74" s="1">
-        <v>18236.0</v>
-      </c>
-    </row>
-    <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="5">
-        <v>45277.0</v>
+      <c r="I74" s="3">
+        <v>18885</v>
+      </c>
+    </row>
+    <row r="75" ht="15.75" customHeight="1" spans="1:9">
+      <c r="A75" s="6">
+        <v>45277</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>130</v>
@@ -2644,18 +3508,18 @@
         <v>19</v>
       </c>
       <c r="F75" s="1">
-        <v>50000.0</v>
+        <v>50000</v>
       </c>
       <c r="G75" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I75" s="1">
-        <v>18238.0</v>
-      </c>
-    </row>
-    <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="5">
-        <v>45282.0</v>
+      <c r="I75" s="3">
+        <v>18415</v>
+      </c>
+    </row>
+    <row r="76" ht="15.75" customHeight="1" spans="1:9">
+      <c r="A76" s="6">
+        <v>45282</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>132</v>
@@ -2670,18 +3534,18 @@
         <v>126</v>
       </c>
       <c r="F76" s="1">
-        <v>50000.0</v>
+        <v>50000</v>
       </c>
       <c r="G76" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I76" s="1">
-        <v>18231.0</v>
-      </c>
-    </row>
-    <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="5">
-        <v>45290.0</v>
+      <c r="I76" s="3">
+        <v>18283</v>
+      </c>
+    </row>
+    <row r="77" ht="15.75" customHeight="1" spans="1:9">
+      <c r="A77" s="6">
+        <v>45290</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>112</v>
@@ -2696,13 +3560,13 @@
         <v>115</v>
       </c>
       <c r="F77" s="1">
-        <v>2000.0</v>
+        <v>2000</v>
       </c>
       <c r="G77" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I77" s="1">
-        <v>729.0</v>
+      <c r="I77" s="3">
+        <v>725</v>
       </c>
     </row>
     <row r="78" ht="15.75" customHeight="1"/>
@@ -3629,9 +4493,8 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
+  <pageSetup paperSize="1" orientation="landscape"/>
+  <headerFooter/>
 </worksheet>
 </file>